--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2475-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2475-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C70F95D-5BBF-48C6-A86D-C3FF9B0DF171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6280ED9-D8D2-4242-8432-9321452FF4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{5237B3A1-B31A-481E-9333-DA78004EE69D}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{C496E014-A313-45B5-9B8F-F205976B3EE1}"/>
   </bookViews>
   <sheets>
     <sheet name="2475-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1466,27 +1466,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A57971D8-ECAA-437A-95CF-2EBCCE22C7AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1507E957-2F66-4C32-9846-609A3B171164}">
   <dimension ref="A1:X29"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1520,7 +1519,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1556,7 +1555,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1608,7 +1607,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1676,7 +1675,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2018</v>
       </c>
@@ -1748,7 +1747,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>2017</v>
       </c>
@@ -1820,7 +1819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>2016</v>
       </c>
@@ -1892,7 +1891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2015</v>
       </c>
@@ -1964,7 +1963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>2014</v>
       </c>
@@ -2036,7 +2035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2013</v>
       </c>
@@ -2108,7 +2107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>2012</v>
       </c>
@@ -2180,7 +2179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2011</v>
       </c>
@@ -2252,7 +2251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>2010</v>
       </c>
@@ -2324,7 +2323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2009</v>
       </c>
@@ -2396,7 +2395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="35">
         <v>2008</v>
       </c>
@@ -2468,7 +2467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2007</v>
       </c>
@@ -2540,7 +2539,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2006</v>
       </c>
@@ -2612,7 +2611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2005</v>
       </c>
@@ -2684,7 +2683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="35">
         <v>2004</v>
       </c>
@@ -2756,7 +2755,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2003</v>
       </c>
@@ -2828,7 +2827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="35">
         <v>2002</v>
       </c>
@@ -2900,7 +2899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2001</v>
       </c>
@@ -2972,7 +2971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>2000</v>
       </c>
@@ -3044,7 +3043,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>1999</v>
       </c>
@@ -3116,7 +3115,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="41"/>
       <c r="B25" s="42"/>
       <c r="C25" s="18" t="s">
@@ -3144,7 +3143,7 @@
       <c r="W25" s="48"/>
       <c r="X25" s="44"/>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>1998</v>
       </c>
@@ -3216,7 +3215,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>1997</v>
       </c>
@@ -3288,7 +3287,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>1996</v>
       </c>
@@ -3360,7 +3359,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37" t="s">
         <v>36</v>
       </c>
